--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-coverage.xlsx
@@ -587,13 +587,13 @@
     <t>insuranceIdentifier</t>
   </si>
   <si>
-    <t>被保険者識別子　例）00012345:あいう:１８７:05</t>
-  </si>
-  <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
-  </si>
-  <si>
-    <t>「被保険者識別子」の文字列仕様を参照のこと</t>
+    <t>被保険者個人識別子　例）00012345:あいう:１８７:05</t>
+  </si>
+  <si>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
     <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
@@ -727,7 +727,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberID</t>
+    <t>http://jpfhir.jp/fhir/clins/Idsystem/JP_Insurance_memberID</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -745,10 +745,10 @@
     <t>Coverage.identifier.value</t>
   </si>
   <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
-本仕様では、以下、これを「被保険者識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
-被保険者識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
-要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者識別子」の文字列仕様を参照のこと</t>
+    <t>被保険者個人識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。詳細は「被保険者個人識別子」の文字列仕様を参照のこと</t>
   </si>
   <si>
     <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
@@ -847,7 +847,7 @@
     <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberCsvID</t>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/JP_Coverage_id</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
